--- a/Testes/reescala/Teste populacao e gerações/Teste9/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste9/3_melhor_escala.xlsx
@@ -1072,8 +1072,8 @@
       <c r="P5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>1</v>
@@ -1081,14 +1081,14 @@
       <c r="S5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>0</v>
+      <c r="T5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="W5" s="5" t="n">
         <v>0</v>
@@ -1183,8 +1183,8 @@
       <c r="P6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
+      <c r="Q6" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>1</v>
@@ -1294,8 +1294,8 @@
       <c r="P7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="5" t="n">
-        <v>0</v>
+      <c r="Q7" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>1</v>
@@ -1960,8 +1960,8 @@
       <c r="P13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" s="4" t="n">
-        <v>1</v>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1</v>
@@ -3118,11 +3118,11 @@
       <c r="AF23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="4" t="n">
-        <v>1</v>
+      <c r="AG23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI23" s="5" t="n">
         <v>0</v>
@@ -3670,11 +3670,11 @@
       <c r="AE28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="5" t="n">
-        <v>0</v>
+      <c r="AF28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AH28" s="5" t="n">
         <v>0</v>
@@ -3865,11 +3865,11 @@
       <c r="V30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" s="5" t="n">
-        <v>0</v>
+      <c r="W30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Y30" s="5" t="n">
         <v>0</v>
@@ -4180,8 +4180,8 @@
       <c r="P33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" s="5" t="n">
-        <v>0</v>
+      <c r="Q33" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R33" s="4" t="n">
         <v>1</v>
@@ -4204,11 +4204,11 @@
       <c r="X33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="5" t="n">
-        <v>0</v>
+      <c r="Y33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="5" t="n">
         <v>0</v>
@@ -4513,8 +4513,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="4" t="n">
-        <v>1</v>
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -4957,8 +4957,8 @@
       <c r="P40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" s="5" t="n">
-        <v>0</v>
+      <c r="Q40" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R40" s="4" t="n">
         <v>1</v>
@@ -5290,8 +5290,8 @@
       <c r="P43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" s="4" t="n">
-        <v>1</v>
+      <c r="Q43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R43" s="5" t="n">
         <v>0</v>
@@ -5302,8 +5302,8 @@
       <c r="T43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="5" t="n">
-        <v>0</v>
+      <c r="U43" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V43" s="5" t="n">
         <v>0</v>
@@ -5869,11 +5869,11 @@
       <c r="X48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="4" t="n">
-        <v>1</v>
+      <c r="Y48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AA48" s="5" t="n">
         <v>0</v>
@@ -5884,20 +5884,20 @@
       <c r="AC48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH48" s="5" t="n">
-        <v>0</v>
+      <c r="AD48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI48" s="5" t="n">
         <v>0</v>
@@ -6106,11 +6106,11 @@
       <c r="AC50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" s="5" t="n">
-        <v>0</v>
+      <c r="AD50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF50" s="5" t="n">
         <v>0</v>
